--- a/Dev_GNC/TableData/Proto/Enum.xlsx
+++ b/Dev_GNC/TableData/Proto/Enum.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\UnityProjects\CardGame\CardGameTable\Table\Proto\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\UnrealProjects\ProjectGNC\Dev_GNC\TableData\Proto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2436AD7-793A-4580-9FA6-B757BB198062}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38807109-8D6F-4F52-A467-8D84A3FE00F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="1560" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -73,9 +73,6 @@
     <t>정찰</t>
   </si>
   <si>
-    <t>ASSULT</t>
-  </si>
-  <si>
     <t>전투</t>
   </si>
   <si>
@@ -360,6 +357,10 @@
   </si>
   <si>
     <t>빈 지역</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ASSAULT</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -742,40 +743,40 @@
     </row>
     <row r="8" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B8" s="1" t="s">
-        <v>17</v>
+        <v>112</v>
       </c>
       <c r="C8" s="1">
         <v>2</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B9" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C9" s="1">
         <v>3</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B10" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C10" s="1">
         <v>4</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>5</v>
@@ -789,62 +790,62 @@
     </row>
     <row r="12" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B12" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C12" s="1">
         <v>1</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B13" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C13" s="1">
         <v>2</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C14" s="1">
         <v>3</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B15" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C15" s="1">
         <v>4</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C16" s="1">
         <v>5</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>5</v>
@@ -858,64 +859,64 @@
     </row>
     <row r="18" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B18" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C18" s="2">
         <v>1</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B19" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C19" s="2">
         <v>2</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B20" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C20" s="2">
         <v>3</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="2"/>
       <c r="B21" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C21" s="2">
         <v>4</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2"/>
       <c r="B22" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C22" s="2">
         <v>5</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>5</v>
@@ -929,40 +930,40 @@
     </row>
     <row r="24" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B24" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C24" s="2">
         <v>1</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B25" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C25" s="2">
         <v>2</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B26" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C26" s="2">
         <v>3</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>5</v>
@@ -976,139 +977,139 @@
     </row>
     <row r="28" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B28" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C28" s="2">
         <v>1</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B29" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C29" s="2">
         <v>2</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B30" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C30" s="2">
         <v>3</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B31" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C31" s="2">
         <v>4</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B32" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C32" s="2">
         <v>5</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B33" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C33" s="2">
         <v>6</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B34" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C34" s="2">
         <v>7</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B35" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C35" s="2">
         <v>8</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B36" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C36" s="2">
         <v>9</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B37" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C37" s="2">
         <v>10</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B38" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C38" s="2">
         <v>11</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="39" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B39" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C39" s="2">
         <v>12</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="40" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>5</v>
@@ -1122,40 +1123,40 @@
     </row>
     <row r="41" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B41" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C41" s="2">
         <v>1</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="42" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B42" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C42" s="2">
         <v>2</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="43" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B43" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C43" s="2">
         <v>3</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="44" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>5</v>
@@ -1170,126 +1171,126 @@
     <row r="45" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="2"/>
       <c r="B45" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C45" s="2">
         <v>1</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="46" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="2"/>
       <c r="B46" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C46" s="2">
         <v>2</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="47" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="2"/>
       <c r="B47" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C47" s="2">
         <v>3</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="48" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="2"/>
       <c r="B48" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C48" s="2">
         <v>4</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="49" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="2"/>
       <c r="B49" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C49" s="2">
         <v>5</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="50" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="2"/>
       <c r="B50" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C50" s="2">
         <v>6</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="51" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="2"/>
       <c r="B51" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C51" s="2">
         <v>7</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="52" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="2"/>
       <c r="B52" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C52" s="2">
         <v>8</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="53" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="2"/>
       <c r="B53" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C53" s="2">
         <v>9</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="54" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="2"/>
       <c r="B54" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C54" s="2">
         <v>10</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="55" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>5</v>
@@ -1303,57 +1304,57 @@
     </row>
     <row r="56" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B56" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C56" s="2">
         <v>1</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="57" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B57" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C57" s="2">
         <v>2</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="58" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B58" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C58" s="2">
         <v>3</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="59" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B59" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C59" s="2">
         <v>4</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="60" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B60" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C60" s="2">
         <v>5</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="61" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
